--- a/xls/square_16_tri3_22.xlsx
+++ b/xls/square_16_tri3_22.xlsx
@@ -482,13 +482,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-2.476545664519621</v>
+        <v>-2.47653828546924</v>
       </c>
       <c r="J22">
-        <v>-1.9858336635394582</v>
+        <v>-1.9858339287894884</v>
       </c>
       <c r="K22">
-        <v>1.5652670320323698</v>
+        <v>1.5652689599377925</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -517,13 +517,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-2.220074096137877</v>
+        <v>-2.220072296134935</v>
       </c>
       <c r="J23">
-        <v>-1.7893490481014211</v>
+        <v>-1.789348963376734</v>
       </c>
       <c r="K23">
-        <v>2.9528997742076317</v>
+        <v>2.9528997191833906</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -552,13 +552,13 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-1.8205662027761182</v>
+        <v>-1.820566265458925</v>
       </c>
       <c r="J24">
-        <v>-1.4358139710724536</v>
+        <v>-1.4358139973699051</v>
       </c>
       <c r="K24">
-        <v>3.2866393296640526</v>
+        <v>3.2866393393689606</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -587,13 +587,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>-0.8121916812395727</v>
+        <v>-0.812191723426751</v>
       </c>
       <c r="J25">
-        <v>-0.6417090906978299</v>
+        <v>-0.641709112167838</v>
       </c>
       <c r="K25">
-        <v>3.766254925917996</v>
+        <v>3.7662549329149666</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -622,13 +622,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-0.46431567307118565</v>
+        <v>-0.4643156784641453</v>
       </c>
       <c r="J26">
-        <v>-0.3965990257929115</v>
+        <v>-0.39659902960695687</v>
       </c>
       <c r="K26">
-        <v>3.915392486683796</v>
+        <v>3.915392488879767</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -657,13 +657,13 @@
         <v>4374</v>
       </c>
       <c r="I27">
-        <v>-0.006386686218326634</v>
+        <v>-0.006386686331482494</v>
       </c>
       <c r="J27">
-        <v>-0.004796369553284691</v>
+        <v>-0.004796369619570115</v>
       </c>
       <c r="K27">
-        <v>3.164688737813319</v>
+        <v>3.1646887385763462</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -692,13 +692,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-0.0023875328207481616</v>
+        <v>-0.0023875328214066948</v>
       </c>
       <c r="J28">
-        <v>-0.001957382615439452</v>
+        <v>-0.0019573826158349656</v>
       </c>
       <c r="K28">
-        <v>3.028843300461393</v>
+        <v>3.0288433005017072</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -727,13 +727,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>-0.002776593445862398</v>
+        <v>-0.002776593442176392</v>
       </c>
       <c r="J29">
-        <v>-0.0024654691319374285</v>
+        <v>-0.0024654691292654357</v>
       </c>
       <c r="K29">
-        <v>3.1008406449000487</v>
+        <v>3.1008406446878767</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -762,13 +762,13 @@
         <v>5400</v>
       </c>
       <c r="I30">
-        <v>-0.0004954360855234768</v>
+        <v>-0.0004954360857399258</v>
       </c>
       <c r="J30">
-        <v>-0.0004376233513341409</v>
+        <v>-0.00043762335147743965</v>
       </c>
       <c r="K30">
-        <v>2.7302380589018655</v>
+        <v>2.730238059062174</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -797,13 +797,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-0.0035395484921898587</v>
+        <v>-0.0035395484937605754</v>
       </c>
       <c r="J31">
-        <v>-0.0026355328861548846</v>
+        <v>-0.0026355328872013878</v>
       </c>
       <c r="K31">
-        <v>3.019268939158852</v>
+        <v>3.0192689394192707</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -832,13 +832,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-0.00039944455988944833</v>
+        <v>-0.0003994445599705746</v>
       </c>
       <c r="J32">
-        <v>-0.00032453667905966933</v>
+        <v>-0.00032453667910927283</v>
       </c>
       <c r="K32">
-        <v>2.6312055472028897</v>
+        <v>2.631205547020442</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_22.xlsx
+++ b/xls/square_16_tri3_22.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>529</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>289</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>2.2453731012814604</v>
+      </c>
+      <c r="J20">
+        <v>-1.1365682174663225</v>
+      </c>
+      <c r="K20">
+        <v>2.810532034970052</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>529</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>289</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>-0.14220970715501666</v>
+      </c>
+      <c r="J21">
+        <v>-2.0519052881159787</v>
+      </c>
+      <c r="K21">
+        <v>1.8481932610275627</v>
+      </c>
+    </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>11</v>
